--- a/jogos_2025-08-17.xlsx
+++ b/jogos_2025-08-17.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="N12" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.14</v>
+        <v>3.35</v>
       </c>
       <c r="M15" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.27</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="N34" t="n">
-        <v>1.79</v>
+        <v>3.04</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="M37" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>3.04</v>
+        <v>2.69</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,16 +5342,16 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.6</v>
+        <v>2.51</v>
       </c>
       <c r="M38" t="n">
-        <v>4.33</v>
+        <v>3.47</v>
       </c>
       <c r="N38" t="n">
-        <v>1.62</v>
+        <v>2.61</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,16 +5474,16 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M40" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="N40" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>12</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N50" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
         <v>0</v>
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9176,10 +9176,10 @@
         <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.2</v>
+        <v>3.84</v>
       </c>
       <c r="M77" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="N77" t="n">
-        <v>2.7</v>
+        <v>2.01</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,16 +11018,16 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF80" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.47</v>
+        <v>1.93</v>
       </c>
       <c r="M81" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N81" t="n">
-        <v>2.85</v>
+        <v>3.13</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.56</v>
+        <v>2.47</v>
       </c>
       <c r="M82" t="n">
-        <v>3.87</v>
+        <v>3.2</v>
       </c>
       <c r="N82" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,16 +11282,16 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="AD82" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,22 +11990,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,22 +12122,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="M101" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N101" t="n">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.19</v>
+        <v>1.59</v>
       </c>
       <c r="M104" t="n">
-        <v>3.23</v>
+        <v>3.92</v>
       </c>
       <c r="N104" t="n">
-        <v>2.82</v>
+        <v>5.3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14318,10 +14318,10 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14762,22 +14762,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14846,10 +14846,10 @@
         <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD109" t="n">
         <v>0</v>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15158,22 +15158,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15554,22 +15554,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="M115" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N115" t="n">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.66</v>
+        <v>2.51</v>
       </c>
       <c r="M118" t="n">
-        <v>3.61</v>
+        <v>3.47</v>
       </c>
       <c r="N118" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.51</v>
+        <v>1.8</v>
       </c>
       <c r="M120" t="n">
         <v>3.47</v>
       </c>
       <c r="N120" t="n">
-        <v>2.6</v>
+        <v>3.62</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16346,22 +16346,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17354,10 +17354,10 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC128" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD128" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.33</v>
+        <v>2.98</v>
       </c>
       <c r="M129" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N129" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="M130" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N130" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17618,10 +17618,10 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.01</v>
+        <v>2.33</v>
       </c>
       <c r="M131" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N131" t="n">
-        <v>2.28</v>
+        <v>2.94</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC131" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AC131" t="n">
-        <v>1.89</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC133" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="M134" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="N134" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC134" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,14 +18230,14 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>6.2</v>
+        <v>1.68</v>
       </c>
       <c r="M135" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N135" t="n">
         <v>4.4</v>
       </c>
-      <c r="N135" t="n">
-        <v>1.44</v>
-      </c>
       <c r="O135" t="n">
         <v>0</v>
       </c>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.45</v>
+        <v>1.89</v>
       </c>
       <c r="M136" t="n">
-        <v>3.27</v>
+        <v>3.65</v>
       </c>
       <c r="N136" t="n">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC136" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,10 +18542,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.89</v>
+        <v>6.2</v>
       </c>
       <c r="M138" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="N138" t="n">
-        <v>3.14</v>
+        <v>1.44</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18674,10 +18674,10 @@
         <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD138" t="n">
         <v>0</v>
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,22 +19514,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19862,16 +19862,16 @@
         <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD147" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF147" t="n">
         <v>0</v>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19946,13 +19946,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19994,16 +19994,16 @@
         <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC148" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD148" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE148" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF148" t="n">
         <v>0</v>
@@ -20042,22 +20042,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20210,13 +20210,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -20258,10 +20258,10 @@
         <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC150" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD150" t="n">
         <v>0</v>
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20474,13 +20474,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20522,10 +20522,10 @@
         <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD152" t="n">
         <v>0</v>
@@ -20570,22 +20570,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20966,22 +20966,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21098,22 +21098,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21446,10 +21446,10 @@
         <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD159" t="n">
         <v>0</v>
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21626,22 +21626,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,22 +21890,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22022,7 +22022,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22058,13 +22058,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -22106,10 +22106,10 @@
         <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD164" t="n">
         <v>0</v>
@@ -22154,22 +22154,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -23078,22 +23078,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23114,13 +23114,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -23162,10 +23162,10 @@
         <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC172" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD172" t="n">
         <v>0</v>
@@ -23210,7 +23210,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23342,22 +23342,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC174" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD174" t="n">
         <v>0</v>
@@ -23474,7 +23474,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23738,22 +23738,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23774,13 +23774,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23822,10 +23822,10 @@
         <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD177" t="n">
         <v>0</v>
@@ -23870,22 +23870,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24002,22 +24002,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -24086,10 +24086,10 @@
         <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD179" t="n">
         <v>0</v>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24170,13 +24170,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24434,13 +24434,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -24530,22 +24530,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24608,16 +24608,16 @@
         <v>0</v>
       </c>
       <c r="Z183" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD183" t="n">
         <v>0</v>
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24830,13 +24830,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24872,16 +24872,16 @@
         <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC185" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD185" t="n">
         <v>0</v>
@@ -24926,22 +24926,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25190,7 +25190,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25454,22 +25454,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25586,22 +25586,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26150,13 +26150,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>1.38</v>
+        <v>2.79</v>
       </c>
       <c r="M195" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="N195" t="n">
-        <v>7.6</v>
+        <v>2.58</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -26198,10 +26198,10 @@
         <v>0</v>
       </c>
       <c r="AB195" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AC195" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="AD195" t="n">
         <v>0</v>
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC197" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26642,22 +26642,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26810,13 +26810,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26858,10 +26858,10 @@
         <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC200" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD200" t="n">
         <v>0</v>
@@ -26906,22 +26906,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC202" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
@@ -27170,22 +27170,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27302,22 +27302,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,13 +27338,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC204" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
@@ -27434,22 +27434,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27566,7 +27566,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="M206" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="N206" t="n">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27650,10 +27650,10 @@
         <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -27698,7 +27698,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27830,22 +27830,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27962,7 +27962,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>3.14</v>
+        <v>5.9</v>
       </c>
       <c r="M209" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N209" t="n">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28046,10 +28046,10 @@
         <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC209" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AD209" t="n">
         <v>0</v>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="M210" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="N210" t="n">
-        <v>1.59</v>
+        <v>5.3</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC210" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.6</v>
+        <v>3.14</v>
       </c>
       <c r="M211" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="N211" t="n">
-        <v>5.3</v>
+        <v>2.07</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,10 +28310,10 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AC211" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AD211" t="n">
         <v>0</v>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="M212" t="n">
-        <v>3.45</v>
+        <v>3.84</v>
       </c>
       <c r="N212" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28442,10 +28442,10 @@
         <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AC212" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AD212" t="n">
         <v>0</v>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28622,22 +28622,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28754,7 +28754,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28764,12 +28764,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28886,7 +28886,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28922,13 +28922,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28970,10 +28970,10 @@
         <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC216" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD216" t="n">
         <v>0</v>
@@ -29018,7 +29018,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -29028,12 +29028,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29054,13 +29054,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29102,10 +29102,10 @@
         <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD217" t="n">
         <v>0</v>
@@ -29150,22 +29150,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29414,22 +29414,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -29556,12 +29556,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29582,13 +29582,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="M221" t="n">
-        <v>3.45</v>
+        <v>3.12</v>
       </c>
       <c r="N221" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -29630,10 +29630,10 @@
         <v>0</v>
       </c>
       <c r="AB221" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC221" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AD221" t="n">
         <v>0</v>
@@ -29678,7 +29678,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="M222" t="n">
         <v>3.15</v>
       </c>
       <c r="N222" t="n">
-        <v>3.52</v>
+        <v>3.95</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29756,16 +29756,16 @@
         <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA222" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB222" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD222" t="n">
         <v>0</v>
@@ -29810,7 +29810,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29820,12 +29820,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29952,12 +29952,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29978,13 +29978,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -30020,10 +30020,10 @@
         <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA224" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB224" t="n">
         <v>0</v>
@@ -30074,22 +30074,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30110,13 +30110,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -30152,10 +30152,10 @@
         <v>0</v>
       </c>
       <c r="Z225" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB225" t="n">
         <v>0</v>
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30242,13 +30242,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30284,10 +30284,10 @@
         <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB226" t="n">
         <v>0</v>
@@ -30338,7 +30338,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30374,13 +30374,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -30422,10 +30422,10 @@
         <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC227" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD227" t="n">
         <v>0</v>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -30480,12 +30480,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30506,13 +30506,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -30554,10 +30554,10 @@
         <v>0</v>
       </c>
       <c r="AB228" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC228" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD228" t="n">
         <v>0</v>
@@ -30602,7 +30602,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -30612,12 +30612,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30638,13 +30638,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -30686,10 +30686,10 @@
         <v>0</v>
       </c>
       <c r="AB229" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC229" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD229" t="n">
         <v>0</v>
@@ -30866,7 +30866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30876,12 +30876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30902,13 +30902,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30950,16 +30950,16 @@
         <v>0</v>
       </c>
       <c r="AB231" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC231" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD231" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE231" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF231" t="n">
         <v>0</v>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -31008,12 +31008,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -31034,13 +31034,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -31082,16 +31082,16 @@
         <v>0</v>
       </c>
       <c r="AB232" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC232" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD232" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE232" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF232" t="n">
         <v>0</v>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -32064,12 +32064,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -32090,13 +32090,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -32144,10 +32144,10 @@
         <v>0</v>
       </c>
       <c r="AD240" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE240" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF240" t="n">
         <v>0</v>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -32196,12 +32196,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -32222,13 +32222,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -32276,10 +32276,10 @@
         <v>0</v>
       </c>
       <c r="AD241" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF241" t="n">
         <v>0</v>
@@ -32318,7 +32318,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -32328,12 +32328,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -32450,7 +32450,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -32460,12 +32460,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G243" t="n">

--- a/jogos_2025-08-17.xlsx
+++ b/jogos_2025-08-17.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.35</v>
+        <v>2.57</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="N15" t="n">
-        <v>1.88</v>
+        <v>2.37</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="M18" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.13</v>
+        <v>2.16</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="M24" t="n">
-        <v>3.47</v>
+        <v>3.38</v>
       </c>
       <c r="N24" t="n">
-        <v>3.57</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4688,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.56</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>1.74</v>
+        <v>2.69</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>3.56</v>
       </c>
       <c r="M34" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>3.04</v>
+        <v>1.74</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4952,10 +4952,10 @@
         <v>2.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.27</v>
+        <v>1.92</v>
       </c>
       <c r="M36" t="n">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="N36" t="n">
-        <v>1.79</v>
+        <v>3.04</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.51</v>
+        <v>12</v>
       </c>
       <c r="M38" t="n">
-        <v>3.47</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.61</v>
+        <v>1.22</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>3.27</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.6</v>
+        <v>2.51</v>
       </c>
       <c r="M40" t="n">
-        <v>4.33</v>
+        <v>3.47</v>
       </c>
       <c r="N40" t="n">
-        <v>1.62</v>
+        <v>2.61</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.27</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N47" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,22 +8822,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,22 +8954,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9176,10 +9176,10 @@
         <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="M70" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="N70" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9968,10 +9968,10 @@
         <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.47</v>
+        <v>2.07</v>
       </c>
       <c r="M82" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="N82" t="n">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.07</v>
+        <v>2.47</v>
       </c>
       <c r="M84" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="N84" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11990,22 +11990,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="M97" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="M98" t="n">
-        <v>3.23</v>
+        <v>3.6</v>
       </c>
       <c r="N98" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="M99" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="N99" t="n">
-        <v>2.04</v>
+        <v>2.63</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,16 +13526,16 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.59</v>
+        <v>2.63</v>
       </c>
       <c r="M104" t="n">
-        <v>3.92</v>
+        <v>3.3</v>
       </c>
       <c r="N104" t="n">
-        <v>5.3</v>
+        <v>2.59</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14762,22 +14762,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14846,10 +14846,10 @@
         <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD109" t="n">
         <v>0</v>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,22 +15158,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,22 +15554,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="M115" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N115" t="n">
-        <v>2.9</v>
+        <v>3.62</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16214,22 +16214,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="M120" t="n">
         <v>3.47</v>
       </c>
       <c r="N120" t="n">
-        <v>3.62</v>
+        <v>2.04</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,16 +16298,16 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF120" t="n">
         <v>0</v>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16688,10 +16688,10 @@
         <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16874,22 +16874,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,10 +16910,10 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="M125" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N125" t="n">
         <v>2.9</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17222,10 +17222,10 @@
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17354,10 +17354,10 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
         <v>0</v>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.45</v>
+        <v>1.89</v>
       </c>
       <c r="M133" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N133" t="n">
-        <v>2.1</v>
+        <v>3.14</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AC133" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.45</v>
+        <v>6.2</v>
       </c>
       <c r="M134" t="n">
-        <v>3.27</v>
+        <v>4.4</v>
       </c>
       <c r="N134" t="n">
-        <v>2.46</v>
+        <v>1.44</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="M135" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="N135" t="n">
-        <v>4.4</v>
+        <v>2.46</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC135" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="M136" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N136" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AC136" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18806,10 +18806,10 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC139" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD139" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19946,13 +19946,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19994,16 +19994,16 @@
         <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD148" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF148" t="n">
         <v>0</v>
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20078,13 +20078,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20126,10 +20126,10 @@
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC149" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD149" t="n">
         <v>0</v>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20210,13 +20210,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -20258,10 +20258,10 @@
         <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC150" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD150" t="n">
         <v>0</v>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,22 +20570,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20834,22 +20834,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -21230,22 +21230,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21446,10 +21446,10 @@
         <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
         <v>0</v>
@@ -21494,22 +21494,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21626,22 +21626,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21710,16 +21710,16 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD161" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF161" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,22 +21890,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -22164,12 +22164,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22418,22 +22418,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22682,7 +22682,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22766,10 +22766,10 @@
         <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC169" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD169" t="n">
         <v>0</v>
@@ -22814,22 +22814,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -23078,22 +23078,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23114,13 +23114,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -23162,10 +23162,10 @@
         <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD172" t="n">
         <v>0</v>
@@ -23210,7 +23210,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23246,13 +23246,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -23294,10 +23294,10 @@
         <v>0</v>
       </c>
       <c r="AB173" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC173" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD173" t="n">
         <v>0</v>
@@ -23342,22 +23342,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23774,13 +23774,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23822,10 +23822,10 @@
         <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD177" t="n">
         <v>0</v>
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24002,22 +24002,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24134,22 +24134,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24170,13 +24170,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -24266,22 +24266,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24530,22 +24530,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24794,22 +24794,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24830,13 +24830,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24872,16 +24872,16 @@
         <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD185" t="n">
         <v>0</v>
@@ -24926,22 +24926,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25058,22 +25058,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25142,10 +25142,10 @@
         <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD187" t="n">
         <v>0</v>
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25454,22 +25454,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25490,13 +25490,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -25532,16 +25532,16 @@
         <v>0</v>
       </c>
       <c r="Z190" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA190" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB190" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC190" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD190" t="n">
         <v>0</v>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25622,13 +25622,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25718,22 +25718,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25850,22 +25850,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="M193" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="N193" t="n">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25934,16 +25934,16 @@
         <v>0</v>
       </c>
       <c r="AB193" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC193" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD193" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AE193" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF193" t="n">
         <v>0</v>
@@ -25982,22 +25982,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26018,13 +26018,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M194" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="N194" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -26066,16 +26066,16 @@
         <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC194" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD194" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF194" t="n">
         <v>0</v>
@@ -26114,22 +26114,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26150,13 +26150,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -26198,10 +26198,10 @@
         <v>0</v>
       </c>
       <c r="AB195" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC195" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD195" t="n">
         <v>0</v>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="M196" t="n">
-        <v>3.59</v>
+        <v>4.7</v>
       </c>
       <c r="N196" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="AC196" t="n">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="AD196" t="n">
         <v>0</v>
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC197" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC198" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26642,22 +26642,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26726,10 +26726,10 @@
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC199" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD199" t="n">
         <v>0</v>
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>2.59</v>
+        <v>1.74</v>
       </c>
       <c r="M202" t="n">
-        <v>3.17</v>
+        <v>3.59</v>
       </c>
       <c r="N202" t="n">
-        <v>2.39</v>
+        <v>4.6</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC202" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
@@ -27170,22 +27170,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27302,22 +27302,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,13 +27338,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC204" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
@@ -27434,22 +27434,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27518,10 +27518,10 @@
         <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC205" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27698,7 +27698,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27830,22 +27830,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27962,7 +27962,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>5.9</v>
+        <v>3.14</v>
       </c>
       <c r="M209" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="N209" t="n">
-        <v>1.51</v>
+        <v>2.07</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28046,10 +28046,10 @@
         <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AC209" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AD209" t="n">
         <v>0</v>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="M210" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N210" t="n">
-        <v>5.3</v>
+        <v>1.51</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC210" t="n">
         <v>1.77</v>
-      </c>
-      <c r="AC210" t="n">
-        <v>2.05</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.14</v>
+        <v>1.6</v>
       </c>
       <c r="M211" t="n">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="N211" t="n">
-        <v>2.07</v>
+        <v>5.3</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,10 +28310,10 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC211" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AD211" t="n">
         <v>0</v>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28922,13 +28922,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28970,10 +28970,10 @@
         <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC216" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD216" t="n">
         <v>0</v>
@@ -29018,7 +29018,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -29028,12 +29028,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29054,13 +29054,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29102,10 +29102,10 @@
         <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC217" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD217" t="n">
         <v>0</v>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -29424,12 +29424,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -29556,12 +29556,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29582,13 +29582,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="M221" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="N221" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -29624,16 +29624,16 @@
         <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA221" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB221" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC221" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD221" t="n">
         <v>0</v>
@@ -29678,7 +29678,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29756,10 +29756,10 @@
         <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB222" t="n">
         <v>0</v>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29952,12 +29952,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29978,13 +29978,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="M224" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N224" t="n">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -30020,16 +30020,16 @@
         <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC224" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD224" t="n">
         <v>0</v>
@@ -30074,22 +30074,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30110,13 +30110,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -30152,10 +30152,10 @@
         <v>0</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB225" t="n">
         <v>0</v>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30242,13 +30242,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30290,10 +30290,10 @@
         <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC226" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD226" t="n">
         <v>0</v>
@@ -30338,7 +30338,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30374,13 +30374,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -30422,10 +30422,10 @@
         <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC227" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD227" t="n">
         <v>0</v>
@@ -30470,22 +30470,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30506,13 +30506,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -30554,10 +30554,10 @@
         <v>0</v>
       </c>
       <c r="AB228" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC228" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD228" t="n">
         <v>0</v>
@@ -30602,7 +30602,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -30612,12 +30612,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30638,13 +30638,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -30686,10 +30686,10 @@
         <v>0</v>
       </c>
       <c r="AB229" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC229" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD229" t="n">
         <v>0</v>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -31536,12 +31536,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31562,13 +31562,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -31604,16 +31604,16 @@
         <v>0</v>
       </c>
       <c r="Z236" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA236" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB236" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC236" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
@@ -31658,7 +31658,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -31668,12 +31668,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31694,13 +31694,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>1.68</v>
+        <v>3.27</v>
       </c>
       <c r="M237" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="N237" t="n">
-        <v>5</v>
+        <v>2.11</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31736,16 +31736,16 @@
         <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB237" t="n">
         <v>2.37</v>
       </c>
-      <c r="AB237" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AC237" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31800,12 +31800,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31826,13 +31826,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31874,10 +31874,10 @@
         <v>0</v>
       </c>
       <c r="AB238" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC238" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD238" t="n">
         <v>0</v>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -32064,12 +32064,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -32090,13 +32090,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -32144,10 +32144,10 @@
         <v>0</v>
       </c>
       <c r="AD240" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF240" t="n">
         <v>0</v>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -32196,12 +32196,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -32222,13 +32222,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -32276,10 +32276,10 @@
         <v>0</v>
       </c>
       <c r="AD241" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE241" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF241" t="n">
         <v>0</v>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -32592,12 +32592,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -32660,16 +32660,16 @@
         <v>0</v>
       </c>
       <c r="Z244" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA244" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB244" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC244" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD244" t="n">
         <v>0</v>
@@ -32714,7 +32714,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -32724,12 +32724,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32750,13 +32750,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32792,16 +32792,16 @@
         <v>0</v>
       </c>
       <c r="Z245" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA245" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB245" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC245" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD245" t="n">
         <v>0</v>

--- a/jogos_2025-08-17.xlsx
+++ b/jogos_2025-08-17.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="M17" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.13</v>
+        <v>1.88</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="M23" t="n">
-        <v>3.47</v>
+        <v>3.38</v>
       </c>
       <c r="N23" t="n">
-        <v>3.57</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="M24" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.89</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.27</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="N32" t="n">
-        <v>1.79</v>
+        <v>3.04</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,16 +4682,16 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.22</v>
+        <v>3.27</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.93</v>
       </c>
       <c r="N33" t="n">
-        <v>2.69</v>
+        <v>1.79</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.56</v>
+        <v>1.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="N34" t="n">
-        <v>1.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.2</v>
+        <v>3.56</v>
       </c>
       <c r="M35" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>8.800000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,16 +5078,16 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.51</v>
+        <v>4.6</v>
       </c>
       <c r="M40" t="n">
-        <v>3.47</v>
+        <v>4.33</v>
       </c>
       <c r="N40" t="n">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="N42" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N48" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8648,10 +8648,10 @@
         <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF62" t="n">
         <v>0</v>
@@ -8690,22 +8690,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,22 +8822,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.2</v>
+        <v>3.84</v>
       </c>
       <c r="M70" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="N70" t="n">
-        <v>2.7</v>
+        <v>2.01</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9968,10 +9968,10 @@
         <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,16 +11018,16 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
         <v>0</v>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.07</v>
+        <v>1.56</v>
       </c>
       <c r="M82" t="n">
-        <v>3.21</v>
+        <v>3.87</v>
       </c>
       <c r="N82" t="n">
-        <v>3.06</v>
+        <v>4.5</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,16 +11282,16 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.93</v>
+        <v>2.47</v>
       </c>
       <c r="M83" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N83" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.47</v>
+        <v>2.07</v>
       </c>
       <c r="M84" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="N84" t="n">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC84" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>1.8</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11990,22 +11990,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,16 +12074,16 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="M94" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>3.85</v>
+        <v>2.63</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,22 +13046,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="M97" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N97" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC97" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="M98" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N98" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="M102" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="N102" t="n">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="M104" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N104" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15764,10 +15764,10 @@
         <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB116" t="n">
         <v>0</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16214,22 +16214,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="M120" t="n">
-        <v>3.47</v>
+        <v>3.15</v>
       </c>
       <c r="N120" t="n">
-        <v>2.04</v>
+        <v>3.85</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,16 +16298,16 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
         <v>0</v>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.89</v>
+        <v>1.9</v>
       </c>
       <c r="M123" t="n">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="N123" t="n">
-        <v>2.89</v>
+        <v>3.7</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16688,10 +16688,10 @@
         <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16874,22 +16874,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="M125" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N125" t="n">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AC125" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,22 +17138,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.51</v>
+        <v>2.03</v>
       </c>
       <c r="M127" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N127" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17222,10 +17222,10 @@
         <v>0</v>
       </c>
       <c r="AB127" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC127" t="n">
         <v>1.86</v>
-      </c>
-      <c r="AC127" t="n">
-        <v>1.84</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3.01</v>
+        <v>2.33</v>
       </c>
       <c r="M130" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N130" t="n">
-        <v>2.28</v>
+        <v>2.94</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17618,10 +17618,10 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC130" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AC130" t="n">
-        <v>1.89</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="M131" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N131" t="n">
-        <v>2.94</v>
+        <v>2.28</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC131" t="n">
         <v>1.89</v>
-      </c>
-      <c r="AC131" t="n">
-        <v>1.85</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="M133" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N133" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AC133" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="M134" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N134" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC134" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.68</v>
+        <v>6.2</v>
       </c>
       <c r="M136" t="n">
-        <v>3.33</v>
+        <v>4.4</v>
       </c>
       <c r="N136" t="n">
-        <v>4.4</v>
+        <v>1.44</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,10 +18542,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>3.45</v>
+        <v>1.89</v>
       </c>
       <c r="M139" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N139" t="n">
-        <v>2.1</v>
+        <v>3.14</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18806,10 +18806,10 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AC139" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD139" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19334,16 +19334,16 @@
         <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF143" t="n">
         <v>0</v>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20078,13 +20078,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20126,10 +20126,10 @@
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD149" t="n">
         <v>0</v>
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20702,22 +20702,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20966,22 +20966,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21098,22 +21098,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21230,22 +21230,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21314,10 +21314,10 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD158" t="n">
         <v>0</v>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21494,22 +21494,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21710,16 +21710,16 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
         <v>0</v>
@@ -21758,22 +21758,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,22 +21890,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22022,22 +22022,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -22164,12 +22164,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22190,13 +22190,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -22238,10 +22238,10 @@
         <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC165" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD165" t="n">
         <v>0</v>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22418,22 +22418,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22682,7 +22682,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22766,10 +22766,10 @@
         <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD169" t="n">
         <v>0</v>
@@ -22814,22 +22814,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -23738,22 +23738,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23870,22 +23870,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -24086,10 +24086,10 @@
         <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD179" t="n">
         <v>0</v>
@@ -24134,22 +24134,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24170,13 +24170,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -24212,16 +24212,16 @@
         <v>0</v>
       </c>
       <c r="Z180" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA180" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB180" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC180" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD180" t="n">
         <v>0</v>
@@ -24266,22 +24266,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24662,22 +24662,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24794,22 +24794,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25058,22 +25058,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25142,10 +25142,10 @@
         <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD187" t="n">
         <v>0</v>
@@ -25190,22 +25190,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25490,13 +25490,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -25532,16 +25532,16 @@
         <v>0</v>
       </c>
       <c r="Z190" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB190" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AC190" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD190" t="n">
         <v>0</v>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25622,13 +25622,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25718,22 +25718,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>1.38</v>
+        <v>2.59</v>
       </c>
       <c r="M196" t="n">
-        <v>4.7</v>
+        <v>3.17</v>
       </c>
       <c r="N196" t="n">
-        <v>7.6</v>
+        <v>2.39</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC196" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AD196" t="n">
         <v>0</v>
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.59</v>
+        <v>1.74</v>
       </c>
       <c r="M198" t="n">
-        <v>3.17</v>
+        <v>3.59</v>
       </c>
       <c r="N198" t="n">
-        <v>2.39</v>
+        <v>4.6</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26642,7 +26642,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26726,10 +26726,10 @@
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC199" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD199" t="n">
         <v>0</v>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26810,13 +26810,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26858,10 +26858,10 @@
         <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC200" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD200" t="n">
         <v>0</v>
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC201" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC202" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
@@ -27170,22 +27170,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27698,22 +27698,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="M209" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="N209" t="n">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28046,10 +28046,10 @@
         <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AC209" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AD209" t="n">
         <v>0</v>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="M210" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N210" t="n">
-        <v>1.51</v>
+        <v>5.3</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC210" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AC210" t="n">
-        <v>1.77</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.6</v>
+        <v>3.14</v>
       </c>
       <c r="M211" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="N211" t="n">
-        <v>5.3</v>
+        <v>2.07</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,10 +28310,10 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AC211" t="n">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="AD211" t="n">
         <v>0</v>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="M212" t="n">
-        <v>3.84</v>
+        <v>3.45</v>
       </c>
       <c r="N212" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28442,10 +28442,10 @@
         <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AC212" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AD212" t="n">
         <v>0</v>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,10 +28574,10 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC213" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD213" t="n">
         <v>0</v>
@@ -28622,22 +28622,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28754,22 +28754,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28886,7 +28886,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -29018,7 +29018,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -29028,12 +29028,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29054,13 +29054,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29102,10 +29102,10 @@
         <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD217" t="n">
         <v>0</v>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -29424,12 +29424,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29450,13 +29450,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -29498,10 +29498,10 @@
         <v>0</v>
       </c>
       <c r="AB220" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC220" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD220" t="n">
         <v>0</v>
@@ -29556,12 +29556,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29582,13 +29582,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="M221" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N221" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -29624,10 +29624,10 @@
         <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AA221" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AB221" t="n">
         <v>0</v>
@@ -29678,7 +29678,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29762,10 +29762,10 @@
         <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC222" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD222" t="n">
         <v>0</v>
@@ -29810,7 +29810,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29820,12 +29820,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29846,13 +29846,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29888,10 +29888,10 @@
         <v>0</v>
       </c>
       <c r="Z223" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB223" t="n">
         <v>0</v>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29952,12 +29952,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29978,13 +29978,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -30026,10 +30026,10 @@
         <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC224" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD224" t="n">
         <v>0</v>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -30084,12 +30084,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30110,13 +30110,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="M225" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N225" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -30152,16 +30152,16 @@
         <v>0</v>
       </c>
       <c r="Z225" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC225" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD225" t="n">
         <v>0</v>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30242,13 +30242,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30290,10 +30290,10 @@
         <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC226" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD226" t="n">
         <v>0</v>
@@ -30338,7 +30338,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30374,13 +30374,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -30422,10 +30422,10 @@
         <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC227" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD227" t="n">
         <v>0</v>
@@ -30602,7 +30602,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -30612,12 +30612,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -31526,7 +31526,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -31536,12 +31536,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31562,13 +31562,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -31604,16 +31604,16 @@
         <v>0</v>
       </c>
       <c r="Z236" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA236" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB236" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC236" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
@@ -31658,7 +31658,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -31668,12 +31668,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31694,13 +31694,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>3.27</v>
+        <v>1.68</v>
       </c>
       <c r="M237" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="N237" t="n">
-        <v>2.11</v>
+        <v>5</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31736,16 +31736,16 @@
         <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA237" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB237" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC237" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31800,12 +31800,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31826,13 +31826,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31874,10 +31874,10 @@
         <v>0</v>
       </c>
       <c r="AB238" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC238" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD238" t="n">
         <v>0</v>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -32196,12 +32196,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -32222,13 +32222,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -32276,10 +32276,10 @@
         <v>0</v>
       </c>
       <c r="AD241" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF241" t="n">
         <v>0</v>
@@ -32318,7 +32318,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -32328,12 +32328,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -32354,13 +32354,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -32408,10 +32408,10 @@
         <v>0</v>
       </c>
       <c r="AD242" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE242" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF242" t="n">
         <v>0</v>
@@ -32450,7 +32450,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -32460,12 +32460,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -32592,12 +32592,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M244" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -32660,16 +32660,16 @@
         <v>0</v>
       </c>
       <c r="Z244" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA244" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB244" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC244" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD244" t="n">
         <v>0</v>
@@ -32714,7 +32714,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -32724,12 +32724,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32750,13 +32750,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N245" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32792,16 +32792,16 @@
         <v>0</v>
       </c>
       <c r="Z245" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA245" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB245" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC245" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD245" t="n">
         <v>0</v>

--- a/jogos_2025-08-17.xlsx
+++ b/jogos_2025-08-17.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1733,10 +1733,10 @@
         <v>2.23</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="M11" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="N11" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.75</v>
+        <v>3.17</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>3.13</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.35</v>
+        <v>2.57</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>1.88</v>
+        <v>2.37</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="M24" t="n">
-        <v>3.47</v>
+        <v>3.38</v>
       </c>
       <c r="N24" t="n">
-        <v>3.57</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,16 +4682,16 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.27</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>3.93</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>1.79</v>
+        <v>2.69</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.2</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>5.8</v>
+        <v>3.68</v>
       </c>
       <c r="N34" t="n">
-        <v>8.800000000000001</v>
+        <v>3.04</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.56</v>
+        <v>1.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="N35" t="n">
-        <v>1.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,16 +5078,16 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.22</v>
+        <v>3.27</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.93</v>
       </c>
       <c r="N37" t="n">
-        <v>2.69</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,16 +5342,16 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>12</v>
+        <v>3.27</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>3.04</v>
       </c>
       <c r="N38" t="n">
-        <v>1.22</v>
+        <v>2.06</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.6</v>
+        <v>2.51</v>
       </c>
       <c r="M40" t="n">
-        <v>4.33</v>
+        <v>3.47</v>
       </c>
       <c r="N40" t="n">
-        <v>1.62</v>
+        <v>2.61</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.51</v>
+        <v>4.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.47</v>
+        <v>4.33</v>
       </c>
       <c r="N42" t="n">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,16 +6002,16 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>12</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.53</v>
+        <v>2.1</v>
       </c>
       <c r="M46" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8162,22 +8162,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8252,10 +8252,10 @@
         <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8648,10 +8648,10 @@
         <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
         <v>0</v>
@@ -8690,22 +8690,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,22 +8954,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9440,10 +9440,10 @@
         <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,16 +11150,16 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF81" t="n">
         <v>0</v>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.56</v>
+        <v>2.07</v>
       </c>
       <c r="M82" t="n">
-        <v>3.87</v>
+        <v>3.21</v>
       </c>
       <c r="N82" t="n">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,16 +11282,16 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="AD82" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
         <v>0</v>
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="M84" t="n">
-        <v>3.21</v>
+        <v>3.55</v>
       </c>
       <c r="N84" t="n">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,22 +11990,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="M88" t="n">
-        <v>3.47</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>2.04</v>
+        <v>3.85</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,16 +12074,16 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.66</v>
+        <v>2.92</v>
       </c>
       <c r="M92" t="n">
-        <v>3.61</v>
+        <v>3.47</v>
       </c>
       <c r="N92" t="n">
-        <v>4.2</v>
+        <v>2.04</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,16 +12602,16 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,22 +13046,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="M102" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N102" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14846,10 +14846,10 @@
         <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD109" t="n">
         <v>0</v>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,22 +15422,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15764,10 +15764,10 @@
         <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
         <v>0</v>
@@ -15818,22 +15818,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="M123" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N123" t="n">
-        <v>3.7</v>
+        <v>2.59</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16874,22 +16874,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.51</v>
+        <v>2.12</v>
       </c>
       <c r="M125" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N125" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AC125" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,22 +17138,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17222,10 +17222,10 @@
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17348,10 +17348,10 @@
         <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB128" t="n">
         <v>0</v>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.68</v>
+        <v>6.2</v>
       </c>
       <c r="M133" t="n">
-        <v>3.33</v>
+        <v>4.4</v>
       </c>
       <c r="N133" t="n">
-        <v>4.4</v>
+        <v>1.44</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3.45</v>
+        <v>1.68</v>
       </c>
       <c r="M134" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="N134" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC134" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.45</v>
+        <v>1.89</v>
       </c>
       <c r="M137" t="n">
-        <v>3.27</v>
+        <v>3.65</v>
       </c>
       <c r="N137" t="n">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,10 +18542,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC137" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.89</v>
+        <v>3.45</v>
       </c>
       <c r="M139" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N139" t="n">
-        <v>3.14</v>
+        <v>2.1</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18806,10 +18806,10 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC139" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AD139" t="n">
         <v>0</v>
@@ -18986,22 +18986,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19334,16 +19334,16 @@
         <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
         <v>0</v>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19682,13 +19682,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19730,16 +19730,16 @@
         <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC146" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD146" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE146" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF146" t="n">
         <v>0</v>
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,22 +19910,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19946,13 +19946,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -20012,10 +20012,10 @@
         <v>0</v>
       </c>
       <c r="AH148" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI148" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20606,13 +20606,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20654,10 +20654,10 @@
         <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC153" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD153" t="n">
         <v>0</v>
@@ -20702,22 +20702,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20834,22 +20834,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20966,22 +20966,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21230,22 +21230,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21314,10 +21314,10 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
         <v>0</v>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21626,22 +21626,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21758,22 +21758,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,22 +21890,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22022,22 +22022,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -22164,12 +22164,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22190,13 +22190,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -22238,10 +22238,10 @@
         <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD165" t="n">
         <v>0</v>
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22634,10 +22634,10 @@
         <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC168" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD168" t="n">
         <v>0</v>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -23738,22 +23738,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23870,22 +23870,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24002,22 +24002,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>3.5</v>
+        <v>2.43</v>
       </c>
       <c r="M179" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="N179" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -24086,10 +24086,10 @@
         <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD179" t="n">
         <v>0</v>
@@ -24134,22 +24134,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24170,13 +24170,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -24212,16 +24212,16 @@
         <v>0</v>
       </c>
       <c r="Z180" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB180" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AC180" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD180" t="n">
         <v>0</v>
@@ -24266,7 +24266,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24302,13 +24302,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24434,13 +24434,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -24482,10 +24482,10 @@
         <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD182" t="n">
         <v>0</v>
@@ -24530,7 +24530,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24830,13 +24830,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24872,16 +24872,16 @@
         <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC185" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD185" t="n">
         <v>0</v>
@@ -25058,22 +25058,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25190,22 +25190,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25586,22 +25586,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25718,7 +25718,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25850,22 +25850,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M193" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="N193" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25934,16 +25934,16 @@
         <v>0</v>
       </c>
       <c r="AB193" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC193" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD193" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AE193" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF193" t="n">
         <v>0</v>
@@ -25982,22 +25982,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26018,13 +26018,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="M194" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="N194" t="n">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -26066,16 +26066,16 @@
         <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC194" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD194" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF194" t="n">
         <v>0</v>
@@ -26114,22 +26114,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD196" t="n">
         <v>0</v>
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC197" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26642,22 +26642,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26810,13 +26810,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="M200" t="n">
-        <v>4.7</v>
+        <v>3.59</v>
       </c>
       <c r="N200" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26858,10 +26858,10 @@
         <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AC200" t="n">
-        <v>2.34</v>
+        <v>1.77</v>
       </c>
       <c r="AD200" t="n">
         <v>0</v>
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC202" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
@@ -27170,22 +27170,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27206,13 +27206,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -27254,10 +27254,10 @@
         <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC203" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD203" t="n">
         <v>0</v>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27434,7 +27434,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="M205" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="N205" t="n">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27518,10 +27518,10 @@
         <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC205" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27566,22 +27566,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27698,22 +27698,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.95</v>
+        <v>4.9</v>
       </c>
       <c r="M207" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N207" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27830,22 +27830,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27962,7 +27962,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="M209" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="N209" t="n">
-        <v>1.59</v>
+        <v>5.3</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28046,10 +28046,10 @@
         <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC209" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AD209" t="n">
         <v>0</v>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="M210" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="N210" t="n">
-        <v>5.3</v>
+        <v>1.59</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AC210" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,10 +28574,10 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC213" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD213" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28886,7 +28886,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -29018,7 +29018,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -29028,12 +29028,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29054,13 +29054,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29102,10 +29102,10 @@
         <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC217" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD217" t="n">
         <v>0</v>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -29424,12 +29424,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29450,13 +29450,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="M220" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="N220" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -29498,10 +29498,10 @@
         <v>0</v>
       </c>
       <c r="AB220" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC220" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD220" t="n">
         <v>0</v>
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -29556,12 +29556,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29582,13 +29582,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="M221" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N221" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -29624,16 +29624,16 @@
         <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB221" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC221" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD221" t="n">
         <v>0</v>
@@ -29678,7 +29678,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="M222" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="N222" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29756,16 +29756,16 @@
         <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA222" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB222" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD222" t="n">
         <v>0</v>
@@ -29820,12 +29820,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29846,13 +29846,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="M223" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N223" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29891,7 +29891,7 @@
         <v>1.6</v>
       </c>
       <c r="AA223" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB223" t="n">
         <v>0</v>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29952,12 +29952,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29978,13 +29978,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -30026,10 +30026,10 @@
         <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC224" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD224" t="n">
         <v>0</v>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -30084,12 +30084,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30110,13 +30110,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -30158,10 +30158,10 @@
         <v>0</v>
       </c>
       <c r="AB225" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC225" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD225" t="n">
         <v>0</v>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30242,13 +30242,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30290,10 +30290,10 @@
         <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC226" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD226" t="n">
         <v>0</v>
@@ -30338,22 +30338,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30470,22 +30470,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30602,7 +30602,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -30612,12 +30612,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30638,13 +30638,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -30680,10 +30680,10 @@
         <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA229" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB229" t="n">
         <v>0</v>
@@ -30770,13 +30770,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30866,7 +30866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30876,12 +30876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30902,13 +30902,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30950,16 +30950,16 @@
         <v>0</v>
       </c>
       <c r="AB231" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC231" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD231" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE231" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF231" t="n">
         <v>0</v>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -31008,12 +31008,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -31034,13 +31034,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -31082,16 +31082,16 @@
         <v>0</v>
       </c>
       <c r="AB232" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC232" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD232" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE232" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF232" t="n">
         <v>0</v>
@@ -31298,13 +31298,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -31340,10 +31340,10 @@
         <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA234" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB234" t="n">
         <v>0</v>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -31536,12 +31536,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31562,13 +31562,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -31610,10 +31610,10 @@
         <v>0</v>
       </c>
       <c r="AB236" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC236" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31800,12 +31800,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31826,13 +31826,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31874,10 +31874,10 @@
         <v>0</v>
       </c>
       <c r="AB238" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC238" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD238" t="n">
         <v>0</v>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -32064,12 +32064,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -32090,13 +32090,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -32144,10 +32144,10 @@
         <v>0</v>
       </c>
       <c r="AD240" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE240" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF240" t="n">
         <v>0</v>
@@ -32318,7 +32318,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -32328,12 +32328,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -32354,13 +32354,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -32408,10 +32408,10 @@
         <v>0</v>
       </c>
       <c r="AD242" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF242" t="n">
         <v>0</v>
@@ -32450,7 +32450,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -32460,12 +32460,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -32486,13 +32486,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>

--- a/jogos_2025-08-17.xlsx
+++ b/jogos_2025-08-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL255"/>
+  <dimension ref="A1:AL256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.51</v>
+        <v>3.18</v>
       </c>
       <c r="N14" t="n">
-        <v>1.71</v>
+        <v>3.13</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.57</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.23</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>2.37</v>
+        <v>2.01</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.56</v>
+        <v>2.22</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>1.74</v>
+        <v>2.69</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,16 +5342,16 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.92</v>
+        <v>1.2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.68</v>
+        <v>5.8</v>
       </c>
       <c r="N39" t="n">
-        <v>3.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,16 +5606,16 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.2</v>
+        <v>3.56</v>
       </c>
       <c r="M40" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>8.800000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.22</v>
+        <v>3.27</v>
       </c>
       <c r="M41" t="n">
-        <v>3.35</v>
+        <v>3.93</v>
       </c>
       <c r="N41" t="n">
-        <v>2.69</v>
+        <v>1.79</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="N44" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.51</v>
+        <v>3.27</v>
       </c>
       <c r="M46" t="n">
-        <v>3.47</v>
+        <v>3.04</v>
       </c>
       <c r="N46" t="n">
-        <v>2.61</v>
+        <v>2.06</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.27</v>
+        <v>2.45</v>
       </c>
       <c r="M47" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="M51" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N51" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8690,22 +8690,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9440,10 +9440,10 @@
         <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9968,10 +9968,10 @@
         <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF72" t="n">
         <v>0</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="M78" t="n">
-        <v>3.57</v>
+        <v>4.6</v>
       </c>
       <c r="N78" t="n">
-        <v>2.78</v>
+        <v>5.5</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10760,10 +10760,10 @@
         <v>0</v>
       </c>
       <c r="AD78" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AF78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.93</v>
+        <v>2.47</v>
       </c>
       <c r="M85" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC85" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>1.9</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.56</v>
+        <v>2.07</v>
       </c>
       <c r="M86" t="n">
-        <v>3.87</v>
+        <v>3.21</v>
       </c>
       <c r="N86" t="n">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,16 +11810,16 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AC86" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AD86" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.07</v>
+        <v>1.56</v>
       </c>
       <c r="M87" t="n">
-        <v>3.21</v>
+        <v>3.87</v>
       </c>
       <c r="N87" t="n">
-        <v>3.06</v>
+        <v>4.5</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,16 +11942,16 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12122,22 +12122,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M101" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="N101" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="M104" t="n">
-        <v>3.92</v>
+        <v>3.15</v>
       </c>
       <c r="N104" t="n">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,16 +14450,16 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15158,22 +15158,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,22 +15290,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="M113" t="n">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="N113" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,16 +15374,16 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC113" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AD113" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
         <v>0</v>
@@ -15422,22 +15422,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.15</v>
+        <v>1.51</v>
       </c>
       <c r="M114" t="n">
-        <v>3.23</v>
+        <v>3.75</v>
       </c>
       <c r="N114" t="n">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,22 +15686,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15770,10 +15770,10 @@
         <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
         <v>0</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="M117" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N117" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16346,22 +16346,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16610,22 +16610,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.65</v>
+        <v>2.03</v>
       </c>
       <c r="M123" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="N123" t="n">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,76 +17042,76 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S126" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T126" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V126" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W126" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X126" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD126" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG126" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH126" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI126" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17793,12 +17793,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -17916,7 +17916,7 @@
         </is>
       </c>
       <c r="AL132" s="3" t="n">
-        <v>45886.51041666666</v>
+        <v>45886.5</v>
       </c>
     </row>
     <row r="133">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.01</v>
+        <v>2.33</v>
       </c>
       <c r="M133" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N133" t="n">
-        <v>2.28</v>
+        <v>2.94</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC133" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>1.89</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="M134" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N134" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC134" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18189,27 +18189,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18312,7 +18312,7 @@
         </is>
       </c>
       <c r="AL135" s="3" t="n">
-        <v>45886.51736111111</v>
+        <v>45886.51041666666</v>
       </c>
     </row>
     <row r="136">
@@ -18321,27 +18321,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18444,7 +18444,7 @@
         </is>
       </c>
       <c r="AL136" s="3" t="n">
-        <v>45886.52083333334</v>
+        <v>45886.51736111111</v>
       </c>
     </row>
     <row r="137">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,10 +18542,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.89</v>
+        <v>6.2</v>
       </c>
       <c r="M138" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="N138" t="n">
-        <v>3.14</v>
+        <v>1.44</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18674,10 +18674,10 @@
         <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD138" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18806,10 +18806,10 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD139" t="n">
         <v>0</v>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD140" t="n">
         <v>0</v>
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.45</v>
+        <v>1.89</v>
       </c>
       <c r="M141" t="n">
-        <v>3.27</v>
+        <v>3.65</v>
       </c>
       <c r="N141" t="n">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -19070,10 +19070,10 @@
         <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC141" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD141" t="n">
         <v>0</v>
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -19202,10 +19202,10 @@
         <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
         <v>0</v>
@@ -19245,12 +19245,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="M143" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N143" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19334,10 +19334,10 @@
         <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD143" t="n">
         <v>0</v>
@@ -19368,7 +19368,7 @@
         </is>
       </c>
       <c r="AL143" s="3" t="n">
-        <v>45886.53125</v>
+        <v>45886.52083333334</v>
       </c>
     </row>
     <row r="144">
@@ -19377,12 +19377,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="AL144" s="3" t="n">
-        <v>45886.54166666666</v>
+        <v>45886.53125</v>
       </c>
     </row>
     <row r="145">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19946,13 +19946,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19994,10 +19994,10 @@
         <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD148" t="n">
         <v>0</v>
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20342,13 +20342,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -20390,16 +20390,16 @@
         <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD151" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
         <v>0</v>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20834,22 +20834,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20870,13 +20870,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20936,10 +20936,10 @@
         <v>0</v>
       </c>
       <c r="AH155" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI155" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
@@ -20966,22 +20966,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21362,22 +21362,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21446,10 +21446,10 @@
         <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD159" t="n">
         <v>0</v>
@@ -21494,22 +21494,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21758,22 +21758,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21860,10 +21860,10 @@
         <v>0</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI162" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21974,10 +21974,10 @@
         <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD163" t="n">
         <v>0</v>
@@ -22286,22 +22286,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,16 +22370,16 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC166" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD166" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE166" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF166" t="n">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22634,10 +22634,10 @@
         <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC168" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD168" t="n">
         <v>0</v>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23337,12 +23337,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="AL174" s="3" t="n">
-        <v>45886.55555555555</v>
+        <v>45886.54166666666</v>
       </c>
     </row>
     <row r="175">
@@ -23469,12 +23469,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23510,13 +23510,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23558,10 +23558,10 @@
         <v>0</v>
       </c>
       <c r="AB175" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD175" t="n">
         <v>0</v>
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="AL175" s="3" t="n">
-        <v>45886.5625</v>
+        <v>45886.55555555555</v>
       </c>
     </row>
     <row r="176">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23642,13 +23642,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23690,10 +23690,10 @@
         <v>0</v>
       </c>
       <c r="AB176" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC176" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD176" t="n">
         <v>0</v>
@@ -23997,12 +23997,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24120,7 +24120,7 @@
         </is>
       </c>
       <c r="AL179" s="3" t="n">
-        <v>45886.57291666666</v>
+        <v>45886.5625</v>
       </c>
     </row>
     <row r="180">
@@ -24129,12 +24129,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="AL180" s="3" t="n">
-        <v>45886.58333333334</v>
+        <v>45886.57291666666</v>
       </c>
     </row>
     <row r="181">
@@ -24266,22 +24266,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24434,13 +24434,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -24482,10 +24482,10 @@
         <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD182" t="n">
         <v>0</v>
@@ -24530,22 +24530,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.08</v>
+        <v>2.85</v>
       </c>
       <c r="M183" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N183" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24614,10 +24614,10 @@
         <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC183" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD183" t="n">
         <v>0</v>
@@ -24662,22 +24662,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24698,13 +24698,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24794,22 +24794,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24962,13 +24962,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -25004,16 +25004,16 @@
         <v>0</v>
       </c>
       <c r="Z186" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB186" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC186" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD186" t="n">
         <v>0</v>
@@ -25058,7 +25058,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25226,13 +25226,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>1.78</v>
+        <v>3.5</v>
       </c>
       <c r="M188" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N188" t="n">
-        <v>5</v>
+        <v>1.87</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -25268,16 +25268,16 @@
         <v>0</v>
       </c>
       <c r="Z188" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB188" t="n">
-        <v>2.47</v>
+        <v>1.8</v>
       </c>
       <c r="AC188" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AD188" t="n">
         <v>0</v>
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25718,22 +25718,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25850,22 +25850,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26114,22 +26114,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26241,27 +26241,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,16 +26330,16 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD196" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
         <v>0</v>
@@ -26364,7 +26364,7 @@
         </is>
       </c>
       <c r="AL196" s="3" t="n">
-        <v>45886.59375</v>
+        <v>45886.58333333334</v>
       </c>
     </row>
     <row r="197">
@@ -26505,27 +26505,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.79</v>
+        <v>2</v>
       </c>
       <c r="M198" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="N198" t="n">
-        <v>2.58</v>
+        <v>2.94</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,16 +26594,16 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.68</v>
+        <v>2.35</v>
       </c>
       <c r="AD198" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE198" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF198" t="n">
         <v>0</v>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="AL198" s="3" t="n">
-        <v>45886.60416666666</v>
+        <v>45886.59375</v>
       </c>
     </row>
     <row r="199">
@@ -26642,22 +26642,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="M199" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="N199" t="n">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26726,10 +26726,10 @@
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC199" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD199" t="n">
         <v>0</v>
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC201" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
@@ -27038,22 +27038,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1.38</v>
+        <v>2.85</v>
       </c>
       <c r="M202" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="N202" t="n">
-        <v>7.6</v>
+        <v>2.12</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC202" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,13 +27338,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC204" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
@@ -27434,7 +27434,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27561,12 +27561,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="M206" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="N206" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27650,10 +27650,10 @@
         <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC206" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -27684,7 +27684,7 @@
         </is>
       </c>
       <c r="AL206" s="3" t="n">
-        <v>45886.625</v>
+        <v>45886.60416666666</v>
       </c>
     </row>
     <row r="207">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27788,10 +27788,10 @@
         <v>0</v>
       </c>
       <c r="AD207" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE207" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF207" t="n">
         <v>0</v>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>4.9</v>
+        <v>2.03</v>
       </c>
       <c r="M209" t="n">
-        <v>4.4</v>
+        <v>2.85</v>
       </c>
       <c r="N209" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28094,22 +28094,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28226,22 +28226,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="M211" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="N211" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28353,12 +28353,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28442,10 +28442,10 @@
         <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD212" t="n">
         <v>0</v>
@@ -28476,7 +28476,7 @@
         </is>
       </c>
       <c r="AL212" s="3" t="n">
-        <v>45886.63541666666</v>
+        <v>45886.625</v>
       </c>
     </row>
     <row r="213">
@@ -28490,7 +28490,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="M213" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="N213" t="n">
-        <v>5.3</v>
+        <v>1.59</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,10 +28574,10 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AC213" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD213" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28658,13 +28658,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="M214" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N214" t="n">
-        <v>1.51</v>
+        <v>5.3</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28706,10 +28706,10 @@
         <v>0</v>
       </c>
       <c r="AB214" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC214" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AC214" t="n">
-        <v>1.77</v>
       </c>
       <c r="AD214" t="n">
         <v>0</v>
@@ -28881,12 +28881,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28922,13 +28922,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28970,10 +28970,10 @@
         <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC216" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD216" t="n">
         <v>0</v>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="AL216" s="3" t="n">
-        <v>45886.64583333334</v>
+        <v>45886.63541666666</v>
       </c>
     </row>
     <row r="217">
@@ -29018,22 +29018,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29054,13 +29054,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29318,13 +29318,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -29366,10 +29366,10 @@
         <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD219" t="n">
         <v>0</v>
@@ -29546,22 +29546,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29582,13 +29582,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -29630,10 +29630,10 @@
         <v>0</v>
       </c>
       <c r="AB221" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC221" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD221" t="n">
         <v>0</v>
@@ -29673,12 +29673,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29762,16 +29762,16 @@
         <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD222" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF222" t="n">
         <v>0</v>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="AL222" s="3" t="n">
-        <v>45886.65625</v>
+        <v>45886.64583333334</v>
       </c>
     </row>
     <row r="223">
@@ -29805,27 +29805,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29846,13 +29846,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>1.74</v>
+        <v>7.9</v>
       </c>
       <c r="M223" t="n">
-        <v>3.12</v>
+        <v>5.6</v>
       </c>
       <c r="N223" t="n">
-        <v>4.5</v>
+        <v>1.31</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29894,16 +29894,16 @@
         <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AC223" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD223" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE223" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF223" t="n">
         <v>0</v>
@@ -29928,7 +29928,7 @@
         </is>
       </c>
       <c r="AL223" s="3" t="n">
-        <v>45886.66666666666</v>
+        <v>45886.65625</v>
       </c>
     </row>
     <row r="224">
@@ -29942,22 +29942,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29978,13 +29978,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -30020,10 +30020,10 @@
         <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA224" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB224" t="n">
         <v>0</v>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -30084,12 +30084,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30110,13 +30110,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30245,10 +30245,10 @@
         <v>1.74</v>
       </c>
       <c r="M226" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="N226" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30284,16 +30284,16 @@
         <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC226" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD226" t="n">
         <v>0</v>
@@ -30338,7 +30338,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30374,13 +30374,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="M227" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="N227" t="n">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -30422,10 +30422,10 @@
         <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC227" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD227" t="n">
         <v>0</v>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -30480,12 +30480,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30506,13 +30506,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -30554,10 +30554,10 @@
         <v>0</v>
       </c>
       <c r="AB228" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC228" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD228" t="n">
         <v>0</v>
@@ -30612,12 +30612,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30638,13 +30638,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="M229" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="N229" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -30680,10 +30680,10 @@
         <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AA229" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB229" t="n">
         <v>0</v>
@@ -30866,7 +30866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30876,12 +30876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30902,13 +30902,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="M231" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="N231" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30944,16 +30944,16 @@
         <v>0</v>
       </c>
       <c r="Z231" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA231" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB231" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC231" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD231" t="n">
         <v>0</v>
@@ -30998,22 +30998,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -31034,13 +31034,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -31082,10 +31082,10 @@
         <v>0</v>
       </c>
       <c r="AB232" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC232" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD232" t="n">
         <v>0</v>
@@ -31125,12 +31125,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -31140,12 +31140,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -31166,13 +31166,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="M233" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="N233" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -31208,10 +31208,10 @@
         <v>0</v>
       </c>
       <c r="Z233" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA233" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB233" t="n">
         <v>0</v>
@@ -31248,7 +31248,7 @@
         </is>
       </c>
       <c r="AL233" s="3" t="n">
-        <v>45886.67708333334</v>
+        <v>45886.66666666666</v>
       </c>
     </row>
     <row r="234">
@@ -31257,27 +31257,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -31298,13 +31298,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="M234" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="N234" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -31346,16 +31346,16 @@
         <v>0</v>
       </c>
       <c r="AB234" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC234" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD234" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AE234" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AF234" t="n">
         <v>0</v>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="AL234" s="3" t="n">
-        <v>45886.6875</v>
+        <v>45886.67708333334</v>
       </c>
     </row>
     <row r="235">
@@ -31562,13 +31562,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -31610,10 +31610,10 @@
         <v>0</v>
       </c>
       <c r="AB236" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC236" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
@@ -31694,13 +31694,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31742,10 +31742,10 @@
         <v>0</v>
       </c>
       <c r="AB237" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC237" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
@@ -31785,27 +31785,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31826,13 +31826,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>2.12</v>
+        <v>1.2</v>
       </c>
       <c r="M238" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="N238" t="n">
-        <v>2.96</v>
+        <v>12</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31874,16 +31874,16 @@
         <v>0</v>
       </c>
       <c r="AB238" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AC238" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AD238" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE238" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF238" t="n">
         <v>0</v>
@@ -31908,7 +31908,7 @@
         </is>
       </c>
       <c r="AL238" s="3" t="n">
-        <v>45886.70833333334</v>
+        <v>45886.6875</v>
       </c>
     </row>
     <row r="239">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -32064,12 +32064,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -32090,13 +32090,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="M240" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N240" t="n">
-        <v>6</v>
+        <v>2.96</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -32132,16 +32132,16 @@
         <v>0</v>
       </c>
       <c r="Z240" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA240" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB240" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC240" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD240" t="n">
         <v>0</v>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="AL240" s="3" t="n">
-        <v>45886.71527777778</v>
+        <v>45886.70833333334</v>
       </c>
     </row>
     <row r="241">
@@ -32181,12 +32181,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -32196,12 +32196,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -32222,13 +32222,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="M241" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N241" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -32264,16 +32264,16 @@
         <v>0</v>
       </c>
       <c r="Z241" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA241" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB241" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC241" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD241" t="n">
         <v>0</v>
@@ -32304,7 +32304,7 @@
         </is>
       </c>
       <c r="AL241" s="3" t="n">
-        <v>45886.75</v>
+        <v>45886.71527777778</v>
       </c>
     </row>
     <row r="242">
@@ -32313,12 +32313,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -32328,12 +32328,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -32354,13 +32354,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="M242" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="N242" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -32396,16 +32396,16 @@
         <v>0</v>
       </c>
       <c r="Z242" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA242" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB242" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC242" t="n">
-        <v>1.46</v>
+        <v>1.95</v>
       </c>
       <c r="AD242" t="n">
         <v>0</v>
@@ -32436,7 +32436,7 @@
         </is>
       </c>
       <c r="AL242" s="3" t="n">
-        <v>45886.77083333334</v>
+        <v>45886.75</v>
       </c>
     </row>
     <row r="243">
@@ -32450,7 +32450,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -32460,12 +32460,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -32486,13 +32486,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N243" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -32534,10 +32534,10 @@
         <v>0</v>
       </c>
       <c r="AB243" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC243" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD243" t="n">
         <v>0</v>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -32592,12 +32592,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M244" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -32660,16 +32660,16 @@
         <v>0</v>
       </c>
       <c r="Z244" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA244" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB244" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC244" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD244" t="n">
         <v>0</v>
@@ -32709,12 +32709,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -32724,12 +32724,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32750,13 +32750,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32798,10 +32798,10 @@
         <v>0</v>
       </c>
       <c r="AB245" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC245" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD245" t="n">
         <v>0</v>
@@ -32832,7 +32832,7 @@
         </is>
       </c>
       <c r="AL245" s="3" t="n">
-        <v>45886.79166666666</v>
+        <v>45886.77083333334</v>
       </c>
     </row>
     <row r="246">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32856,12 +32856,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32988,12 +32988,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -33014,13 +33014,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -33056,10 +33056,10 @@
         <v>0</v>
       </c>
       <c r="Z247" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA247" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB247" t="n">
         <v>0</v>
@@ -33105,12 +33105,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -33200,10 +33200,10 @@
         <v>0</v>
       </c>
       <c r="AD248" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF248" t="n">
         <v>0</v>
@@ -33228,7 +33228,7 @@
         </is>
       </c>
       <c r="AL248" s="3" t="n">
-        <v>45886.83333333334</v>
+        <v>45886.79166666666</v>
       </c>
     </row>
     <row r="249">
@@ -33242,7 +33242,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -33252,12 +33252,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -33278,13 +33278,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M249" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -33374,7 +33374,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -33384,12 +33384,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -33410,13 +33410,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -33506,7 +33506,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -33542,13 +33542,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -33596,10 +33596,10 @@
         <v>0</v>
       </c>
       <c r="AD251" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE251" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF251" t="n">
         <v>0</v>
@@ -33633,12 +33633,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -33648,12 +33648,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33674,13 +33674,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -33716,16 +33716,16 @@
         <v>0</v>
       </c>
       <c r="Z252" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB252" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC252" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD252" t="n">
         <v>0</v>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="AL252" s="3" t="n">
-        <v>45886.85416666666</v>
+        <v>45886.83333333334</v>
       </c>
     </row>
     <row r="253">
@@ -33897,12 +33897,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33912,12 +33912,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33938,13 +33938,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1.7</v>
+        <v>2.27</v>
       </c>
       <c r="M254" t="n">
-        <v>3.85</v>
+        <v>2.84</v>
       </c>
       <c r="N254" t="n">
-        <v>5</v>
+        <v>3.06</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33980,16 +33980,16 @@
         <v>0</v>
       </c>
       <c r="Z254" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA254" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB254" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC254" t="n">
-        <v>2.13</v>
+        <v>1.55</v>
       </c>
       <c r="AD254" t="n">
         <v>0</v>
@@ -34020,7 +34020,7 @@
         </is>
       </c>
       <c r="AL254" s="3" t="n">
-        <v>45886.91666666666</v>
+        <v>45886.85416666666</v>
       </c>
     </row>
     <row r="255">
@@ -34029,129 +34029,261 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L255" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M255" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N255" t="n">
+        <v>5</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>0</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0</v>
+      </c>
+      <c r="S255" t="n">
+        <v>0</v>
+      </c>
+      <c r="T255" t="n">
+        <v>0</v>
+      </c>
+      <c r="U255" t="n">
+        <v>0</v>
+      </c>
+      <c r="V255" t="n">
+        <v>0</v>
+      </c>
+      <c r="W255" t="n">
+        <v>0</v>
+      </c>
+      <c r="X255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL255" s="3" t="n">
+        <v>45886.91666666666</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>45886</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E256" t="inlineStr">
         <is>
           <t>Real Monarchs</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
+      <c r="F256" t="inlineStr">
         <is>
           <t>Los Angeles II</t>
         </is>
       </c>
-      <c r="G255" t="n">
-        <v>0</v>
-      </c>
-      <c r="H255" t="n">
-        <v>0</v>
-      </c>
-      <c r="I255" t="n">
-        <v>0</v>
-      </c>
-      <c r="J255" t="n">
-        <v>0</v>
-      </c>
-      <c r="K255" t="inlineStr">
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L255" t="n">
-        <v>0</v>
-      </c>
-      <c r="M255" t="n">
-        <v>0</v>
-      </c>
-      <c r="N255" t="n">
-        <v>0</v>
-      </c>
-      <c r="O255" t="n">
-        <v>0</v>
-      </c>
-      <c r="P255" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
-      <c r="R255" t="n">
-        <v>0</v>
-      </c>
-      <c r="S255" t="n">
-        <v>0</v>
-      </c>
-      <c r="T255" t="n">
-        <v>0</v>
-      </c>
-      <c r="U255" t="n">
-        <v>0</v>
-      </c>
-      <c r="V255" t="n">
-        <v>0</v>
-      </c>
-      <c r="W255" t="n">
-        <v>0</v>
-      </c>
-      <c r="X255" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y255" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z255" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA255" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB255" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC255" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD255" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE255" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF255" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG255" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH255" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI255" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL255" s="3" t="n">
+      <c r="L256" t="n">
+        <v>0</v>
+      </c>
+      <c r="M256" t="n">
+        <v>0</v>
+      </c>
+      <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>0</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="n">
+        <v>0</v>
+      </c>
+      <c r="T256" t="n">
+        <v>0</v>
+      </c>
+      <c r="U256" t="n">
+        <v>0</v>
+      </c>
+      <c r="V256" t="n">
+        <v>0</v>
+      </c>
+      <c r="W256" t="n">
+        <v>0</v>
+      </c>
+      <c r="X256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL256" s="3" t="n">
         <v>45886.9375</v>
       </c>
     </row>

--- a/jogos_2025-08-17.xlsx
+++ b/jogos_2025-08-17.xlsx
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="M14" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="N14" t="n">
-        <v>3.13</v>
+        <v>2.37</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>3.13</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.12</v>
+        <v>3.51</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>2.14</v>
       </c>
       <c r="M19" t="n">
-        <v>3.51</v>
+        <v>3.12</v>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="M36" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>3.04</v>
+        <v>2.69</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="N37" t="n">
-        <v>2.69</v>
+        <v>3.04</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,16 +5342,16 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.2</v>
+        <v>3.27</v>
       </c>
       <c r="M39" t="n">
-        <v>5.8</v>
+        <v>3.93</v>
       </c>
       <c r="N39" t="n">
-        <v>8.800000000000001</v>
+        <v>1.79</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5612,10 +5612,10 @@
         <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5876,10 +5876,10 @@
         <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>12</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.27</v>
+        <v>12</v>
       </c>
       <c r="M46" t="n">
-        <v>3.04</v>
+        <v>6</v>
       </c>
       <c r="N46" t="n">
-        <v>2.06</v>
+        <v>1.22</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.45</v>
+        <v>3.27</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="N47" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.58</v>
+        <v>3.53</v>
       </c>
       <c r="M51" t="n">
-        <v>4.3</v>
+        <v>3.53</v>
       </c>
       <c r="N51" t="n">
-        <v>5.4</v>
+        <v>1.99</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="M52" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="M72" t="n">
-        <v>3.57</v>
+        <v>3.39</v>
       </c>
       <c r="N72" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,16 +9962,16 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10313,10 +10313,10 @@
         <v>2.09</v>
       </c>
       <c r="M75" t="n">
-        <v>3.3</v>
+        <v>3.57</v>
       </c>
       <c r="N75" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,16 +10358,16 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF75" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10760,10 +10760,10 @@
         <v>0</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11156,10 +11156,10 @@
         <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF81" t="n">
         <v>0</v>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.47</v>
+        <v>1.93</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N85" t="n">
-        <v>2.85</v>
+        <v>3.13</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,16 +11942,16 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="M89" t="n">
-        <v>3.55</v>
+        <v>3.87</v>
       </c>
       <c r="N89" t="n">
-        <v>3.13</v>
+        <v>4.5</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,16 +12206,16 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF89" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="M99" t="n">
-        <v>3.23</v>
+        <v>3.6</v>
       </c>
       <c r="N99" t="n">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="M102" t="n">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="N102" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AC102" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="M104" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="N104" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="M105" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N105" t="n">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="M106" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="N106" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,16 +14450,16 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC106" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AD106" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
         <v>0</v>
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.59</v>
+        <v>2.03</v>
       </c>
       <c r="M107" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="N107" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15026,22 +15026,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15158,22 +15158,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,22 +15686,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="M117" t="n">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="N117" t="n">
-        <v>5.25</v>
+        <v>3.62</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,76 +16250,76 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V120" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W120" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X120" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG120" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH120" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI120" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
@@ -16346,22 +16346,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16610,22 +16610,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="M123" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N123" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,76 +17042,76 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X126" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH126" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AI126" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="M129" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="N129" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17798,22 +17798,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17882,16 +17882,16 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC132" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD132" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE132" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF132" t="n">
         <v>0</v>
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.33</v>
+        <v>2.98</v>
       </c>
       <c r="M133" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N133" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AC133" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.98</v>
+        <v>2.33</v>
       </c>
       <c r="M135" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="N135" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AC135" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,10 +18542,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,14 +18626,14 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>6.2</v>
+        <v>1.68</v>
       </c>
       <c r="M138" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N138" t="n">
         <v>4.4</v>
       </c>
-      <c r="N138" t="n">
-        <v>1.44</v>
-      </c>
       <c r="O138" t="n">
         <v>0</v>
       </c>
@@ -18674,10 +18674,10 @@
         <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC138" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD138" t="n">
         <v>0</v>
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.45</v>
+        <v>6.2</v>
       </c>
       <c r="M140" t="n">
-        <v>3.27</v>
+        <v>4.4</v>
       </c>
       <c r="N140" t="n">
-        <v>2.46</v>
+        <v>1.44</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD140" t="n">
         <v>0</v>
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -19202,10 +19202,10 @@
         <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD142" t="n">
         <v>0</v>
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20870,13 +20870,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20936,10 +20936,10 @@
         <v>0</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI155" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21002,13 +21002,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -21068,10 +21068,10 @@
         <v>0</v>
       </c>
       <c r="AH156" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI156" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
@@ -21098,22 +21098,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21446,10 +21446,10 @@
         <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
         <v>0</v>
@@ -21494,22 +21494,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21974,16 +21974,16 @@
         <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC163" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD163" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE163" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF163" t="n">
         <v>0</v>
@@ -22022,22 +22022,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,16 +22370,16 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD166" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF166" t="n">
         <v>0</v>
@@ -22418,22 +22418,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22682,7 +22682,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC174" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD174" t="n">
         <v>0</v>
@@ -23870,22 +23870,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24002,22 +24002,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24434,13 +24434,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -24482,10 +24482,10 @@
         <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD182" t="n">
         <v>0</v>
@@ -24530,22 +24530,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24614,10 +24614,10 @@
         <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD183" t="n">
         <v>0</v>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24794,22 +24794,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24926,22 +24926,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24962,13 +24962,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>1.78</v>
+        <v>2.85</v>
       </c>
       <c r="M186" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N186" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -25004,16 +25004,16 @@
         <v>0</v>
       </c>
       <c r="Z186" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB186" t="n">
-        <v>2.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC186" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AD186" t="n">
         <v>0</v>
@@ -25058,7 +25058,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25226,13 +25226,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>3.5</v>
+        <v>1.78</v>
       </c>
       <c r="M188" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N188" t="n">
-        <v>1.87</v>
+        <v>5</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -25268,16 +25268,16 @@
         <v>0</v>
       </c>
       <c r="Z188" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA188" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB188" t="n">
-        <v>1.8</v>
+        <v>2.47</v>
       </c>
       <c r="AC188" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AD188" t="n">
         <v>0</v>
@@ -25454,22 +25454,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25586,22 +25586,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25718,22 +25718,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25850,22 +25850,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26114,22 +26114,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26378,22 +26378,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="M197" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="N197" t="n">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,16 +26462,16 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC197" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD197" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AE197" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF197" t="n">
         <v>0</v>
@@ -26510,22 +26510,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M198" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="N198" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,16 +26594,16 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC198" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD198" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AE198" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF198" t="n">
         <v>0</v>
@@ -26642,7 +26642,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26726,10 +26726,10 @@
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC199" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD199" t="n">
         <v>0</v>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26810,13 +26810,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26858,10 +26858,10 @@
         <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC200" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD200" t="n">
         <v>0</v>
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC201" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
@@ -27038,22 +27038,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="M202" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="N202" t="n">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC202" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
@@ -27170,22 +27170,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27206,13 +27206,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1.74</v>
+        <v>2.85</v>
       </c>
       <c r="M203" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="N203" t="n">
-        <v>4.6</v>
+        <v>2.12</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -27254,10 +27254,10 @@
         <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC203" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD203" t="n">
         <v>0</v>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,13 +27338,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC204" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
@@ -27434,7 +27434,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27518,10 +27518,10 @@
         <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC205" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27566,7 +27566,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27650,10 +27650,10 @@
         <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -27698,22 +27698,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27788,10 +27788,10 @@
         <v>0</v>
       </c>
       <c r="AD207" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF207" t="n">
         <v>0</v>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27840,12 +27840,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27866,13 +27866,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="M208" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="N208" t="n">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27914,10 +27914,10 @@
         <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC208" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD208" t="n">
         <v>0</v>
@@ -27962,22 +27962,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="M209" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="N209" t="n">
-        <v>3.9</v>
+        <v>3.17</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28046,10 +28046,10 @@
         <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC209" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD209" t="n">
         <v>0</v>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28226,22 +28226,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28358,22 +28358,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28448,10 +28448,10 @@
         <v>0</v>
       </c>
       <c r="AD212" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF212" t="n">
         <v>0</v>
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="M213" t="n">
-        <v>3.84</v>
+        <v>3.14</v>
       </c>
       <c r="N213" t="n">
-        <v>1.59</v>
+        <v>2.07</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,10 +28574,10 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AC213" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AD213" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28658,13 +28658,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="M214" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="N214" t="n">
-        <v>5.3</v>
+        <v>1.59</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28706,10 +28706,10 @@
         <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AC214" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD214" t="n">
         <v>0</v>
@@ -28754,7 +28754,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28764,12 +28764,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28790,13 +28790,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>3.14</v>
+        <v>5.9</v>
       </c>
       <c r="M215" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N215" t="n">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28838,10 +28838,10 @@
         <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AC215" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AD215" t="n">
         <v>0</v>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28922,13 +28922,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="M216" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N216" t="n">
-        <v>1.51</v>
+        <v>5.3</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28970,10 +28970,10 @@
         <v>0</v>
       </c>
       <c r="AB216" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC216" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AC216" t="n">
-        <v>1.77</v>
       </c>
       <c r="AD216" t="n">
         <v>0</v>
@@ -29018,22 +29018,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29054,13 +29054,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29414,22 +29414,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29450,13 +29450,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -29556,12 +29556,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29582,13 +29582,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -29630,10 +29630,10 @@
         <v>0</v>
       </c>
       <c r="AB221" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC221" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD221" t="n">
         <v>0</v>
@@ -29678,7 +29678,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29762,10 +29762,10 @@
         <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC222" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD222" t="n">
         <v>0</v>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29952,12 +29952,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29978,13 +29978,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -30020,10 +30020,10 @@
         <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB224" t="n">
         <v>0</v>
@@ -30084,12 +30084,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30110,13 +30110,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="M225" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="N225" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -30152,10 +30152,10 @@
         <v>0</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB225" t="n">
         <v>0</v>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30242,13 +30242,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.74</v>
+        <v>3.05</v>
       </c>
       <c r="M226" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="N226" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30284,16 +30284,16 @@
         <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA226" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB226" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC226" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD226" t="n">
         <v>0</v>
@@ -30338,7 +30338,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30374,13 +30374,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="M227" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N227" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -30416,16 +30416,16 @@
         <v>0</v>
       </c>
       <c r="Z227" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA227" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB227" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC227" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD227" t="n">
         <v>0</v>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -30480,12 +30480,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30506,13 +30506,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -30554,10 +30554,10 @@
         <v>0</v>
       </c>
       <c r="AB228" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC228" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD228" t="n">
         <v>0</v>
@@ -30612,12 +30612,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30638,13 +30638,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="M229" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="N229" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -30680,10 +30680,10 @@
         <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
         <v>0</v>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30744,12 +30744,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30770,13 +30770,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30818,10 +30818,10 @@
         <v>0</v>
       </c>
       <c r="AB230" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC230" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD230" t="n">
         <v>0</v>
@@ -30866,7 +30866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30876,12 +30876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30902,13 +30902,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30950,10 +30950,10 @@
         <v>0</v>
       </c>
       <c r="AB231" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC231" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD231" t="n">
         <v>0</v>
@@ -30998,22 +30998,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -31034,13 +31034,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -31082,10 +31082,10 @@
         <v>0</v>
       </c>
       <c r="AB232" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC232" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD232" t="n">
         <v>0</v>
@@ -31130,22 +31130,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -31166,13 +31166,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -31208,10 +31208,10 @@
         <v>0</v>
       </c>
       <c r="Z233" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA233" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB233" t="n">
         <v>0</v>
@@ -31526,22 +31526,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31562,13 +31562,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2.32</v>
+        <v>1.2</v>
       </c>
       <c r="M236" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="N236" t="n">
-        <v>2.95</v>
+        <v>12</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -31610,16 +31610,16 @@
         <v>0</v>
       </c>
       <c r="AB236" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC236" t="n">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="AD236" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE236" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF236" t="n">
         <v>0</v>
@@ -31668,12 +31668,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31694,13 +31694,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>1.6</v>
+        <v>2.32</v>
       </c>
       <c r="M237" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N237" t="n">
-        <v>5.43</v>
+        <v>2.95</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31742,10 +31742,10 @@
         <v>0</v>
       </c>
       <c r="AB237" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AC237" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
@@ -31790,22 +31790,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31826,13 +31826,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="M238" t="n">
-        <v>6.5</v>
+        <v>3.55</v>
       </c>
       <c r="N238" t="n">
-        <v>12</v>
+        <v>5.43</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31874,16 +31874,16 @@
         <v>0</v>
       </c>
       <c r="AB238" t="n">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="AC238" t="n">
-        <v>2.35</v>
+        <v>1.54</v>
       </c>
       <c r="AD238" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF238" t="n">
         <v>0</v>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31932,12 +31932,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31958,13 +31958,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="M239" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N239" t="n">
-        <v>7</v>
+        <v>2.96</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -32006,10 +32006,10 @@
         <v>0</v>
       </c>
       <c r="AB239" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AC239" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AD239" t="n">
         <v>0</v>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -32064,12 +32064,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -32090,13 +32090,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="M240" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N240" t="n">
-        <v>2.96</v>
+        <v>7</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -32138,10 +32138,10 @@
         <v>0</v>
       </c>
       <c r="AB240" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AC240" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AD240" t="n">
         <v>0</v>
@@ -32450,7 +32450,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -32460,12 +32460,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -32486,13 +32486,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -32534,10 +32534,10 @@
         <v>0</v>
       </c>
       <c r="AB243" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC243" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD243" t="n">
         <v>0</v>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -32592,12 +32592,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -32660,16 +32660,16 @@
         <v>0</v>
       </c>
       <c r="Z244" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA244" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB244" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC244" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AD244" t="n">
         <v>0</v>
@@ -32714,7 +32714,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -32724,12 +32724,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32750,13 +32750,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>3.27</v>
+        <v>1.68</v>
       </c>
       <c r="M245" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="N245" t="n">
-        <v>2.11</v>
+        <v>5</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32792,16 +32792,16 @@
         <v>0</v>
       </c>
       <c r="Z245" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA245" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB245" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC245" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AD245" t="n">
         <v>0</v>
@@ -32846,7 +32846,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32856,12 +32856,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -33374,7 +33374,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -33384,12 +33384,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -33542,13 +33542,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -33596,10 +33596,10 @@
         <v>0</v>
       </c>
       <c r="AD251" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF251" t="n">
         <v>0</v>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -33648,12 +33648,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33674,13 +33674,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -33728,10 +33728,10 @@
         <v>0</v>
       </c>
       <c r="AD252" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE252" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF252" t="n">
         <v>0</v>
@@ -33770,7 +33770,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33780,12 +33780,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33806,13 +33806,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M253" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -33848,16 +33848,16 @@
         <v>0</v>
       </c>
       <c r="Z253" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA253" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB253" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC253" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD253" t="n">
         <v>0</v>
@@ -33902,7 +33902,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33912,12 +33912,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33938,13 +33938,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33980,16 +33980,16 @@
         <v>0</v>
       </c>
       <c r="Z254" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA254" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB254" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC254" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD254" t="n">
         <v>0</v>

--- a/jogos_2025-08-17.xlsx
+++ b/jogos_2025-08-17.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.23</v>
+        <v>3.51</v>
       </c>
       <c r="N13" t="n">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="M14" t="n">
-        <v>3.51</v>
+        <v>3.23</v>
       </c>
       <c r="N14" t="n">
-        <v>1.71</v>
+        <v>2.37</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="M16" t="n">
-        <v>3.39</v>
+        <v>3.17</v>
       </c>
       <c r="N16" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.92</v>
+        <v>1.2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.68</v>
+        <v>5.8</v>
       </c>
       <c r="N37" t="n">
-        <v>3.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,16 +5342,16 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.2</v>
+        <v>3.56</v>
       </c>
       <c r="M39" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>8.800000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,16 +5606,16 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.56</v>
+        <v>1.92</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="N41" t="n">
-        <v>1.74</v>
+        <v>3.04</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5876,10 +5876,10 @@
         <v>2.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>12</v>
+        <v>3.27</v>
       </c>
       <c r="M43" t="n">
-        <v>6</v>
+        <v>3.04</v>
       </c>
       <c r="N43" t="n">
-        <v>1.22</v>
+        <v>2.06</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.27</v>
+        <v>4.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.04</v>
+        <v>4.33</v>
       </c>
       <c r="N44" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,16 +6266,16 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,16 +6398,16 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.53</v>
+        <v>2.1</v>
       </c>
       <c r="M53" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -8162,22 +8162,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10100,10 +10100,10 @@
         <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF73" t="n">
         <v>0</v>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10496,10 +10496,10 @@
         <v>0</v>
       </c>
       <c r="AD76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.66</v>
+        <v>3.84</v>
       </c>
       <c r="M77" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="N77" t="n">
-        <v>4.7</v>
+        <v>2.01</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.56</v>
+        <v>2.47</v>
       </c>
       <c r="M83" t="n">
-        <v>3.87</v>
+        <v>3.2</v>
       </c>
       <c r="N83" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,16 +11414,16 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.07</v>
+        <v>1.56</v>
       </c>
       <c r="M87" t="n">
-        <v>3.21</v>
+        <v>3.87</v>
       </c>
       <c r="N87" t="n">
-        <v>3.06</v>
+        <v>4.5</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,16 +11942,16 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF87" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="M93" t="n">
-        <v>3.92</v>
+        <v>3.15</v>
       </c>
       <c r="N93" t="n">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.66</v>
+        <v>2.63</v>
       </c>
       <c r="M95" t="n">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="N95" t="n">
-        <v>4.2</v>
+        <v>2.59</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,22 +13046,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,76 +13082,76 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.15</v>
+        <v>2.89</v>
       </c>
       <c r="M96" t="n">
-        <v>3.23</v>
+        <v>2.78</v>
       </c>
       <c r="N96" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.79</v>
+        <v>2.7</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI96" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.88</v>
+        <v>2.65</v>
       </c>
       <c r="M98" t="n">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
       <c r="N98" t="n">
-        <v>3.85</v>
+        <v>2.23</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,22 +13574,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13706,22 +13706,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,16 +13922,16 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF102" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="M104" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N104" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14318,10 +14318,10 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
         <v>0</v>
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.92</v>
+        <v>1.8</v>
       </c>
       <c r="M106" t="n">
         <v>3.47</v>
       </c>
       <c r="N106" t="n">
-        <v>2.04</v>
+        <v>3.62</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,16 +14450,16 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14846,10 +14846,10 @@
         <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD109" t="n">
         <v>0</v>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15026,22 +15026,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15554,22 +15554,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,76 +15722,76 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V116" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH116" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AI116" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,22 +15950,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.03</v>
+        <v>1.51</v>
       </c>
       <c r="M118" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N118" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,22 +16214,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="M120" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="N120" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16478,22 +16478,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,14 +16646,14 @@
         </is>
       </c>
       <c r="L123" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M123" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N123" t="n">
         <v>2.63</v>
       </c>
-      <c r="M123" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N123" t="n">
-        <v>2.59</v>
-      </c>
       <c r="O123" t="n">
         <v>0</v>
       </c>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="M132" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N132" t="n">
-        <v>2.94</v>
+        <v>2.28</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC132" t="n">
         <v>1.89</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>1.85</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.01</v>
+        <v>2.33</v>
       </c>
       <c r="M133" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N133" t="n">
-        <v>2.28</v>
+        <v>2.94</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC133" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>1.89</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>6.2</v>
+        <v>1.89</v>
       </c>
       <c r="M137" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="N137" t="n">
-        <v>1.44</v>
+        <v>3.14</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,10 +18542,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.89</v>
+        <v>6.2</v>
       </c>
       <c r="M138" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="N138" t="n">
-        <v>3.14</v>
+        <v>1.44</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18674,10 +18674,10 @@
         <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD138" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18806,10 +18806,10 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD139" t="n">
         <v>0</v>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>3.45</v>
+        <v>1.68</v>
       </c>
       <c r="M140" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="N140" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC140" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AD140" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="M141" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="N141" t="n">
-        <v>4.4</v>
+        <v>2.46</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -19070,10 +19070,10 @@
         <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC141" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AD141" t="n">
         <v>0</v>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,22 +19646,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19682,13 +19682,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19730,10 +19730,10 @@
         <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD146" t="n">
         <v>0</v>
@@ -19778,22 +19778,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19880,10 +19880,10 @@
         <v>0</v>
       </c>
       <c r="AH147" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI147" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20210,13 +20210,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -20258,10 +20258,10 @@
         <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC150" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD150" t="n">
         <v>0</v>
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20438,22 +20438,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20702,22 +20702,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21314,16 +21314,16 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF158" t="n">
         <v>0</v>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21446,10 +21446,10 @@
         <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD159" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,22 +21890,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22022,22 +22022,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22154,22 +22154,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22190,13 +22190,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -22238,16 +22238,16 @@
         <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC165" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD165" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE165" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF165" t="n">
         <v>0</v>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,10 +22370,10 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD166" t="n">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22550,22 +22550,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22652,10 +22652,10 @@
         <v>0</v>
       </c>
       <c r="AH168" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI168" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23606,22 +23606,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23738,22 +23738,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -24002,22 +24002,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24266,22 +24266,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,22 +24398,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24530,22 +24530,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24662,22 +24662,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24698,13 +24698,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24794,22 +24794,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24962,13 +24962,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -25004,16 +25004,16 @@
         <v>0</v>
       </c>
       <c r="Z186" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB186" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AC186" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD186" t="n">
         <v>0</v>
@@ -25058,22 +25058,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25226,13 +25226,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -25268,16 +25268,16 @@
         <v>0</v>
       </c>
       <c r="Z188" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA188" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB188" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC188" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD188" t="n">
         <v>0</v>
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25454,7 +25454,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25490,13 +25490,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -25538,10 +25538,10 @@
         <v>0</v>
       </c>
       <c r="AB190" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD190" t="n">
         <v>0</v>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25850,7 +25850,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25934,10 +25934,10 @@
         <v>0</v>
       </c>
       <c r="AB193" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD193" t="n">
         <v>0</v>
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC197" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26642,7 +26642,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26726,10 +26726,10 @@
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC199" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD199" t="n">
         <v>0</v>
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC202" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27206,13 +27206,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -27254,10 +27254,10 @@
         <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC203" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD203" t="n">
         <v>0</v>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,13 +27338,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC204" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
@@ -27434,22 +27434,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27518,10 +27518,10 @@
         <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC205" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27566,22 +27566,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27698,22 +27698,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="M207" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="N207" t="n">
-        <v>1.55</v>
+        <v>3.4</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27788,10 +27788,10 @@
         <v>0</v>
       </c>
       <c r="AD207" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF207" t="n">
         <v>0</v>
@@ -27830,22 +27830,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27866,13 +27866,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="M208" t="n">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="N208" t="n">
-        <v>3.17</v>
+        <v>3.9</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27914,10 +27914,10 @@
         <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC208" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD208" t="n">
         <v>0</v>
@@ -27962,22 +27962,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28094,22 +28094,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28184,10 +28184,10 @@
         <v>0</v>
       </c>
       <c r="AD210" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE210" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF210" t="n">
         <v>0</v>
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="M211" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="N211" t="n">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,10 +28310,10 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AC211" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AD211" t="n">
         <v>0</v>
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="M212" t="n">
-        <v>3.84</v>
+        <v>3.14</v>
       </c>
       <c r="N212" t="n">
-        <v>1.59</v>
+        <v>2.07</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28442,10 +28442,10 @@
         <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AC212" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AD212" t="n">
         <v>0</v>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="M213" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N213" t="n">
-        <v>1.51</v>
+        <v>5.3</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,10 +28574,10 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC213" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AC213" t="n">
-        <v>1.77</v>
       </c>
       <c r="AD213" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28658,13 +28658,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="M214" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N214" t="n">
-        <v>5.3</v>
+        <v>1.51</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28706,10 +28706,10 @@
         <v>0</v>
       </c>
       <c r="AB214" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC214" t="n">
         <v>1.77</v>
-      </c>
-      <c r="AC214" t="n">
-        <v>2.05</v>
       </c>
       <c r="AD214" t="n">
         <v>0</v>
@@ -28754,7 +28754,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28764,12 +28764,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28790,13 +28790,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28838,10 +28838,10 @@
         <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC215" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD215" t="n">
         <v>0</v>
@@ -29018,22 +29018,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29054,13 +29054,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29318,13 +29318,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -29366,10 +29366,10 @@
         <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD219" t="n">
         <v>0</v>
@@ -29414,22 +29414,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29450,13 +29450,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -29678,7 +29678,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="M222" t="n">
-        <v>3.12</v>
+        <v>2.65</v>
       </c>
       <c r="N222" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29756,16 +29756,16 @@
         <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA222" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB222" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD222" t="n">
         <v>0</v>
@@ -29810,7 +29810,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29820,12 +29820,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29849,10 +29849,10 @@
         <v>1.74</v>
       </c>
       <c r="M223" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="N223" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29888,16 +29888,16 @@
         <v>0</v>
       </c>
       <c r="Z223" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC223" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD223" t="n">
         <v>0</v>
@@ -29942,22 +29942,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29978,13 +29978,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -30084,12 +30084,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30110,13 +30110,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -30158,10 +30158,10 @@
         <v>0</v>
       </c>
       <c r="AB225" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC225" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD225" t="n">
         <v>0</v>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30242,13 +30242,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>3.05</v>
+        <v>1.93</v>
       </c>
       <c r="M226" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="N226" t="n">
-        <v>2.6</v>
+        <v>3.52</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30284,16 +30284,16 @@
         <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC226" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD226" t="n">
         <v>0</v>
@@ -30338,7 +30338,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30374,13 +30374,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="M227" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N227" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -30422,10 +30422,10 @@
         <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC227" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD227" t="n">
         <v>0</v>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -30480,12 +30480,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30506,13 +30506,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="M228" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="N228" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -30548,16 +30548,16 @@
         <v>0</v>
       </c>
       <c r="Z228" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA228" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB228" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC228" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD228" t="n">
         <v>0</v>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30744,12 +30744,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30770,13 +30770,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30812,10 +30812,10 @@
         <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA230" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB230" t="n">
         <v>0</v>
@@ -30866,22 +30866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30902,13 +30902,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30944,10 +30944,10 @@
         <v>0</v>
       </c>
       <c r="Z231" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA231" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB231" t="n">
         <v>0</v>
@@ -31130,22 +31130,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -31166,13 +31166,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>5.43</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -31214,10 +31214,10 @@
         <v>0</v>
       </c>
       <c r="AB233" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC233" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD233" t="n">
         <v>0</v>
@@ -31262,22 +31262,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -31298,13 +31298,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>1.2</v>
+        <v>2.32</v>
       </c>
       <c r="M234" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="N234" t="n">
-        <v>12</v>
+        <v>2.95</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -31346,16 +31346,16 @@
         <v>0</v>
       </c>
       <c r="AB234" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC234" t="n">
-        <v>2.35</v>
+        <v>1.58</v>
       </c>
       <c r="AD234" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF234" t="n">
         <v>0</v>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -31404,12 +31404,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -31430,13 +31430,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -31478,16 +31478,16 @@
         <v>0</v>
       </c>
       <c r="AB235" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC235" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD235" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE235" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF235" t="n">
         <v>0</v>
@@ -31536,12 +31536,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31562,13 +31562,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2.32</v>
+        <v>1.6</v>
       </c>
       <c r="M236" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N236" t="n">
-        <v>2.95</v>
+        <v>5.43</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -31610,10 +31610,10 @@
         <v>0</v>
       </c>
       <c r="AB236" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC236" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
@@ -31658,7 +31658,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -31668,12 +31668,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31694,13 +31694,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="M237" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N237" t="n">
-        <v>2.96</v>
+        <v>7</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31742,10 +31742,10 @@
         <v>0</v>
       </c>
       <c r="AB237" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AC237" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31800,12 +31800,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31826,13 +31826,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="M238" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N238" t="n">
-        <v>7</v>
+        <v>2.96</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31874,10 +31874,10 @@
         <v>0</v>
       </c>
       <c r="AB238" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AC238" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AD238" t="n">
         <v>0</v>
@@ -32592,12 +32592,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M244" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -32660,10 +32660,10 @@
         <v>0</v>
       </c>
       <c r="Z244" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA244" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB244" t="n">
         <v>0</v>
@@ -32724,12 +32724,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32750,13 +32750,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N245" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32792,10 +32792,10 @@
         <v>0</v>
       </c>
       <c r="Z245" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA245" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB245" t="n">
         <v>0</v>
@@ -32978,7 +32978,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32988,12 +32988,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -33014,13 +33014,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -33200,10 +33200,10 @@
         <v>0</v>
       </c>
       <c r="AD248" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF248" t="n">
         <v>0</v>
@@ -33242,7 +33242,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -33252,12 +33252,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -33374,7 +33374,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -33384,12 +33384,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -33410,13 +33410,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="M250" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N250" t="n">
-        <v>4.85</v>
+        <v>2.5</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -33464,10 +33464,10 @@
         <v>0</v>
       </c>
       <c r="AD250" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE250" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF250" t="n">
         <v>0</v>
@@ -33506,7 +33506,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -33542,13 +33542,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -33584,16 +33584,16 @@
         <v>0</v>
       </c>
       <c r="Z251" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA251" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB251" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC251" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD251" t="n">
         <v>0</v>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -33648,12 +33648,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33674,13 +33674,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -33716,16 +33716,16 @@
         <v>0</v>
       </c>
       <c r="Z252" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB252" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC252" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD252" t="n">
         <v>0</v>
